--- a/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_보완필요_담당자별확인요청표_20261008.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_보완필요_담당자별확인요청표_20261008.xlsx
@@ -16,11 +16,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="한상돈" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="김주태" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="박철호" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사무실" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="이은주&#10;박철호" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="품질팀" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안종명" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="미지정" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="이은주·박철호(공동)" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안종명" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="담당자 미지정" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'지성규'!$A$3:$M$57</definedName>
@@ -31,12 +29,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'한상돈'!$A$3:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'김주태'!$A$3:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'박철호'!$A$3:$M$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'사무실'!$A$3:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'이은주
-박철호'!$A$3:$M$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'품질팀'!$A$3:$M$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'안종명'!$A$3:$M$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'미지정'!$A$3:$M$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'이은주·박철호(공동)'!$A$3:$M$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'안종명'!$A$3:$M$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'담당자 미지정'!$A$3:$M$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -506,112 +501,104 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>'담당자 미지정' 시트: 담당자 칸이 공란이거나 부서명(사무실·품질팀)만 적힌 건으로, 담당자 지정이 먼저 필요합니다.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>담당자별 건수:</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  지성규: 54건</t>
+          <t>담당자별 건수:</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  이광재: 33건</t>
+          <t xml:space="preserve">  지성규: 54건</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  김명용: 28건</t>
+          <t xml:space="preserve">  이광재: 33건</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  이은주: 19건</t>
+          <t xml:space="preserve">  김명용: 28건</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  황지환: 14건</t>
+          <t xml:space="preserve">  이은주: 19건</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  한상돈: 8건</t>
+          <t xml:space="preserve">  황지환: 14건</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  김주태: 6건</t>
+          <t xml:space="preserve">  한상돈: 8건</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  박철호: 4건</t>
+          <t xml:space="preserve">  김주태: 6건</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  사무실: 3건</t>
+          <t xml:space="preserve">  박철호: 4건</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  이은주
-박철호: 1건</t>
+          <t xml:space="preserve">  이은주·박철호(공동): 1건</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  품질팀: 1건</t>
+          <t xml:space="preserve">  안종명: 1건</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  안종명: 1건</t>
+          <t xml:space="preserve">  담당자 미지정: 21건</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (미지정): 17건</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>합계 189건</t>
         </is>
@@ -628,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -649,7 +636,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>사무실 담당 확인 요청 (3건)</t>
+          <t>이은주·박철호(공동) 담당 확인 요청 (1건)</t>
         </is>
       </c>
     </row>
@@ -722,42 +709,41 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>129</v>
+        <v>30</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>금형관리</t>
+          <t>검사시험</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>금형이관 T/O보고서</t>
+          <t>원자재 검사협정서  OR 검사기준서</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>SH-FM-251</t>
+          <t>SH-FM-152</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>SH-FM-251</t>
+          <t>SH-FM-152</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>SH-FM-249-253/Rev00</t>
+          <t>SH-FM-152-159/Rev00</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>신규제작 금형 이관시 T/OUT 성형 검증 실시(실시결과 증빙관리)
-      ※ 자체 프레스 공정이 없는경우 미해당으로 표기</t>
+          <t>검사협정서/기준서 체결상태</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -770,114 +756,10 @@
       <c r="L4" s="4" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>금형관리</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>4-5</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>금형이관시 접수자료</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>SH-FM-252</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>SH-FM-252</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>SH-FM-249-253/Rev00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>점검·검사 항목과 기준(기준서는 본문)을 작성해 주세요.</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>131</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>금형관리</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>4-5</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>금형문제점개선자료</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>SH-FM-253</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>SH-FM-253</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>SH-FM-249-253/Rev00</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>점검·검사 항목과 기준(기준서는 본문)을 작성해 주세요.</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:M6"/>
-  <dataValidations count="3">
+  <autoFilter ref="A3:M4"/>
+  <dataValidations count="1">
     <dataValidation sqref="J4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"작성 예정(예정일 메모),작성 완료(파일 제출),기존 사용 양식 있음(파일 제출),대표 양식으로 충족,분리 필요,기타(메모 기재)"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"작성 예정(예정일 메모),작성 완료(파일 제출),기존 사용 양식 있음(파일 제출),대표 양식으로 충족,분리 필요,기타(메모 기재)"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"작성 예정(예정일 메모),작성 완료(파일 제출),기존 사용 양식 있음(파일 제출),대표 양식으로 충족,분리 필요,기타(메모 기재)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -912,8 +794,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>이은주
-박철호 담당 확인 요청 (1건)</t>
+          <t>안종명 담당 확인 요청 (1건)</t>
         </is>
       </c>
     </row>
@@ -986,41 +867,41 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>30</v>
+        <v>234</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>검사시험</t>
+          <t>품질경영체제</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>6-12</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>원자재 검사협정서  OR 검사기준서</t>
+          <t>자격인증내 실기평가보고서첨부</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>SH-FM-152</t>
+          <t>SH-FM-356</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>SH-FM-152</t>
+          <t>SH-FM-356</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>SH-FM-152-159/Rev00</t>
+          <t>SH-FM-356/Rev00</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>검사협정서/기준서 체결상태</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -1050,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1071,323 +952,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>품질팀 담당 확인 요청 (1건)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>SQ NO</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>분야</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>필요서류</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>배정 FM</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>대표 FM</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>릴리스 위치(05_FINAL/RELEASED)</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>요구사항(세부 추진 항목)</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>확인 요청 내용</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>작성 상태</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>메모(예정일 등)</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>확인자</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>확인일</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>214</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>품질경영체제</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>6-8</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>D+3개월 유효성검증</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>SH-FM-336</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>SH-FM-336</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>SH-FM-327-336/Rev00</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>점검·검사 항목과 기준(기준서는 본문)을 작성해 주세요.</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:M4"/>
-  <dataValidations count="1">
-    <dataValidation sqref="J4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"작성 예정(예정일 메모),작성 완료(파일 제출),기존 사용 양식 있음(파일 제출),대표 양식으로 충족,분리 필요,기타(메모 기재)"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>안종명 담당 확인 요청 (1건)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>SQ NO</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>분야</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>필요서류</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>배정 FM</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>대표 FM</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>릴리스 위치(05_FINAL/RELEASED)</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>요구사항(세부 추진 항목)</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>확인 요청 내용</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>작성 상태</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>메모(예정일 등)</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>확인자</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>확인일</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>234</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>품질경영체제</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>6-12</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>자격인증내 실기평가보고서첨부</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>SH-FM-356</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>SH-FM-356</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>SH-FM-356/Rev00</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>점검·검사 항목과 기준(기준서는 본문)을 작성해 주세요.</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:M4"/>
-  <dataValidations count="1">
-    <dataValidation sqref="J4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"작성 예정(예정일 메모),작성 완료(파일 제출),기존 사용 양식 있음(파일 제출),대표 양식으로 충족,분리 필요,기타(메모 기재)"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>(미지정) 담당 확인 요청 (17건)</t>
+          <t>담당자 미지정 담당 확인 요청 (21건)</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1068,11 @@
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>담당자 칸 공란 — 담당자 지정 필요</t>
+        </is>
+      </c>
       <c r="L4" s="4" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr"/>
     </row>
@@ -1552,7 +1121,11 @@
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>담당자 칸 공란 — 담당자 지정 필요</t>
+        </is>
+      </c>
       <c r="L5" s="4" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr"/>
     </row>
@@ -1601,7 +1174,11 @@
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>담당자 칸 공란 — 담당자 지정 필요</t>
+        </is>
+      </c>
       <c r="L6" s="4" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr"/>
     </row>
@@ -1650,7 +1227,11 @@
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>담당자 칸 공란 — 담당자 지정 필요</t>
+        </is>
+      </c>
       <c r="L7" s="4" t="inlineStr"/>
       <c r="M7" s="4" t="inlineStr"/>
     </row>
@@ -1699,7 +1280,11 @@
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>담당자 칸 공란 — 담당자 지정 필요</t>
+        </is>
+      </c>
       <c r="L8" s="4" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr"/>
     </row>
@@ -1748,7 +1333,11 @@
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>담당자 칸 공란 — 담당자 지정 필요</t>
+        </is>
+      </c>
       <c r="L9" s="4" t="inlineStr"/>
       <c r="M9" s="4" t="inlineStr"/>
     </row>
@@ -1797,7 +1386,11 @@
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>담당자 칸 공란 — 담당자 지정 필요</t>
+        </is>
+      </c>
       <c r="L10" s="4" t="inlineStr"/>
       <c r="M10" s="4" t="inlineStr"/>
     </row>
@@ -1846,7 +1439,11 @@
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>담당자 칸 공란 — 담당자 지정 필요</t>
+        </is>
+      </c>
       <c r="L11" s="4" t="inlineStr"/>
       <c r="M11" s="4" t="inlineStr"/>
     </row>
@@ -1895,7 +1492,11 @@
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>담당자 칸 공란 — 담당자 지정 필요</t>
+        </is>
+      </c>
       <c r="L12" s="4" t="inlineStr"/>
       <c r="M12" s="4" t="inlineStr"/>
     </row>
@@ -1944,7 +1545,11 @@
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>담당자 칸 공란 — 담당자 지정 필요</t>
+        </is>
+      </c>
       <c r="L13" s="4" t="inlineStr"/>
       <c r="M13" s="4" t="inlineStr"/>
     </row>
@@ -1993,7 +1598,11 @@
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>담당자 칸 공란 — 담당자 지정 필요</t>
+        </is>
+      </c>
       <c r="L14" s="4" t="inlineStr"/>
       <c r="M14" s="4" t="inlineStr"/>
     </row>
@@ -2042,7 +1651,11 @@
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>담당자 칸 공란 — 담당자 지정 필요</t>
+        </is>
+      </c>
       <c r="L15" s="4" t="inlineStr"/>
       <c r="M15" s="4" t="inlineStr"/>
     </row>
@@ -2091,7 +1704,11 @@
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>담당자 칸 공란 — 담당자 지정 필요</t>
+        </is>
+      </c>
       <c r="L16" s="4" t="inlineStr"/>
       <c r="M16" s="4" t="inlineStr"/>
     </row>
@@ -2140,7 +1757,11 @@
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>담당자 칸 공란 — 담당자 지정 필요</t>
+        </is>
+      </c>
       <c r="L17" s="4" t="inlineStr"/>
       <c r="M17" s="4" t="inlineStr"/>
     </row>
@@ -2189,7 +1810,11 @@
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>담당자 칸 공란 — 담당자 지정 필요</t>
+        </is>
+      </c>
       <c r="L18" s="4" t="inlineStr"/>
       <c r="M18" s="4" t="inlineStr"/>
     </row>
@@ -2238,7 +1863,11 @@
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>담당자 칸 공란 — 담당자 지정 필요</t>
+        </is>
+      </c>
       <c r="L19" s="4" t="inlineStr"/>
       <c r="M19" s="4" t="inlineStr"/>
     </row>
@@ -2287,13 +1916,230 @@
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>담당자 칸 공란 — 담당자 지정 필요</t>
+        </is>
+      </c>
       <c r="L20" s="4" t="inlineStr"/>
       <c r="M20" s="4" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>금형관리</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>금형이관 T/O보고서</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>SH-FM-251</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>SH-FM-251</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>SH-FM-249-253/Rev00</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>신규제작 금형 이관시 T/OUT 성형 검증 실시(실시결과 증빙관리)
+      ※ 자체 프레스 공정이 없는경우 미해당으로 표기</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>점검·검사 항목과 기준(기준서는 본문)을 작성해 주세요.</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>필요서류 정리 파일의 담당자 칸에 부서명 '사무실'만 기재 — 담당자 지정 필요</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr"/>
+      <c r="M21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>금형관리</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>금형이관시 접수자료</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>SH-FM-252</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>SH-FM-252</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>SH-FM-249-253/Rev00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>점검·검사 항목과 기준(기준서는 본문)을 작성해 주세요.</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>필요서류 정리 파일의 담당자 칸에 부서명 '사무실'만 기재 — 담당자 지정 필요</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr"/>
+      <c r="M22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>금형관리</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>금형문제점개선자료</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>SH-FM-253</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>SH-FM-253</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>SH-FM-249-253/Rev00</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>점검·검사 항목과 기준(기준서는 본문)을 작성해 주세요.</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>필요서류 정리 파일의 담당자 칸에 부서명 '사무실'만 기재 — 담당자 지정 필요</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr"/>
+      <c r="M23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>214</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>품질경영체제</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>6-8</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>D+3개월 유효성검증</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>SH-FM-336</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>SH-FM-336</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>SH-FM-327-336/Rev00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>점검·검사 항목과 기준(기준서는 본문)을 작성해 주세요.</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>필요서류 정리 파일의 담당자 칸에 부서명 '품질팀'만 기재 — 담당자 지정 필요</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr"/>
+      <c r="M24" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:M20"/>
-  <dataValidations count="17">
+  <autoFilter ref="A3:M24"/>
+  <dataValidations count="21">
     <dataValidation sqref="J4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"작성 예정(예정일 메모),작성 완료(파일 제출),기존 사용 양식 있음(파일 제출),대표 양식으로 충족,분리 필요,기타(메모 기재)"</formula1>
     </dataValidation>
@@ -2343,6 +2189,18 @@
       <formula1>"작성 예정(예정일 메모),작성 완료(파일 제출),기존 사용 양식 있음(파일 제출),대표 양식으로 충족,분리 필요,기타(메모 기재)"</formula1>
     </dataValidation>
     <dataValidation sqref="J20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"작성 예정(예정일 메모),작성 완료(파일 제출),기존 사용 양식 있음(파일 제출),대표 양식으로 충족,분리 필요,기타(메모 기재)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"작성 예정(예정일 메모),작성 완료(파일 제출),기존 사용 양식 있음(파일 제출),대표 양식으로 충족,분리 필요,기타(메모 기재)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"작성 예정(예정일 메모),작성 완료(파일 제출),기존 사용 양식 있음(파일 제출),대표 양식으로 충족,분리 필요,기타(메모 기재)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"작성 예정(예정일 메모),작성 완료(파일 제출),기존 사용 양식 있음(파일 제출),대표 양식으로 충족,분리 필요,기타(메모 기재)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"작성 예정(예정일 메모),작성 완료(파일 제출),기존 사용 양식 있음(파일 제출),대표 양식으로 충족,분리 필요,기타(메모 기재)"</formula1>
     </dataValidation>
   </dataValidations>
